--- a/docentes/Santiago Hernández Mariana - Estadisticos 20241.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -70,7 +70,13 @@
     <t>CORTES</t>
   </si>
   <si>
-    <t>ACATECATL</t>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>AREVALO</t>
@@ -79,16 +85,25 @@
     <t>CANSECO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>ALISON</t>
   </si>
   <si>
-    <t>MARIA NATHALIE</t>
+    <t>NATHAN KARLO</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>CRISTOFER FRANCISCO</t>
   </si>
   <si>
     <t>ALBA DANIELA</t>
@@ -557,16 +572,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>86.11</v>
+      </c>
+      <c r="H2">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -622,16 +640,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>86.11</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -641,7 +659,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -679,10 +697,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -696,16 +714,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920151</v>
+        <v>24330051920216</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -714,21 +732,21 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920358</v>
+        <v>24330051920359</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -737,6 +755,52 @@
         <v>9</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24330051920163</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920358</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20241.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -67,46 +67,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>AREVALO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>ALISON</t>
-  </si>
-  <si>
-    <t>NATHAN KARLO</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
     <t>CRISTOFER FRANCISCO</t>
-  </si>
-  <si>
-    <t>ALBA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -640,16 +607,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>86.11</v>
+        <v>94.44</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -691,16 +658,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920160</v>
+        <v>24330051920163</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -709,98 +676,6 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>24330051920216</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>24330051920359</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920163</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920358</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>
